--- a/results/supplement/Supplementary_Tables.xlsx
+++ b/results/supplement/Supplementary_Tables.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LAMP result: 1 = positive (uidA: &lt;= 30 min and &gt;= 3-fold; papGII: &lt;= 23 min and &gt;= 3-fold); time to threshold empty = fluorescence threshold not reached within 40 min. Bacterial density from semi-quantitative culture of 10 ul; the category 10^5 includes &gt;10^5 CFU/ml. papG alleles: BLASTN vs papG classes I-IV (&gt;= 90% identity, &gt;= 80% coverage); phylogroups: EzClermont.</t>
+          <t>LAMP result: 1 = positive (uidA: &lt;= 30 min and &gt;= 3-fold; papGII: &lt;= 23 min and &gt;= 3-fold); time to threshold empty = fluorescence threshold not reached within 40 min. Bacterial density from semi-quantitative culture of 10 ul (categories &lt;10^4, 10^4, 10^5 and &gt;10^5 CFU/ml). papG alleles: BLASTN vs papG classes I-IV (&gt;= 90% identity, &gt;= 80% coverage); phylogroups: EzClermont.</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10^4</t>
+          <t>&lt;10^4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>10^4</t>
+          <t>&lt;10^4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10^4</t>
+          <t>&lt;10^4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10^4</t>
+          <t>&lt;10^4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -13807,7 +13807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14605,7 +14605,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>&gt;10^5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10^5 (includes &gt;10^5)</t>
+          <t>10^5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -14970,131 +14970,166 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2. uidA TTT by papGII status</t>
+          <t xml:space="preserve">  category 10^4: n=4 median=28.5 IQR=25.0-29.2 range=16-30 never_crossed=0; papGII-positive: 0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  all loads: papGII+ n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
+          <t xml:space="preserve">  category 10^5: n=7 median=27.5 IQR=26.2-29.5 range=21-33 never_crossed=1; papGII-positive: 1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  all loads: papGII- n=32 median=24.0 IQR=19.5-28.0 range=14-36 never_crossed=1</t>
+          <t xml:space="preserve">  category &gt;10^5: n=27 median=21.0 IQR=18.5-26.0 range=14-36 never_crossed=0; papGII-positive: 5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  all loads: Mann-Whitney p = 0.273</t>
+          <t xml:space="preserve">  &gt;10^5 vs &lt;=10^5 CFU/ml: n=27 median=21.0 IQR=18.5-26.0 range=14-36 never_crossed=0 vs n=11 median=28.0 IQR=26.2-29.8 range=16-33 never_crossed=1; Mann-Whitney p = 0.028</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;=10^5 CFU/ml: papGII+ n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
+          <t xml:space="preserve">  within &gt;10^5 CFU/ml: papGII+ n=5 median=21.0 IQR=18.0-26.0 range=18-26 never_crossed=0 vs papGII- n=22 median=21.5 IQR=19.0-25.8 range=14-36 never_crossed=0; Mann-Whitney p = 0.729</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;=10^5 CFU/ml: papGII- n=28 median=22.0 IQR=19.5-27.5 range=14-36 never_crossed=1</t>
+          <t>2. uidA TTT by papGII status</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;=10^5 CFU/ml: Mann-Whitney p = 0.336</t>
+          <t xml:space="preserve">  all loads: papGII+ n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3. papGII vs uidA primer set in papGII-positive urines (paired)</t>
+          <t xml:space="preserve">  all loads: papGII- n=32 median=24.0 IQR=19.5-28.0 range=14-36 never_crossed=1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  papGII primers: n=6 median=17.0 IQR=16.0-18.0 range=13-20 never_crossed=0</t>
+          <t xml:space="preserve">  all loads: Mann-Whitney p = 0.273</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  uidA primers:   n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
+          <t xml:space="preserve">  &gt;=10^5 CFU/ml: papGII+ n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">  papGII earlier in 6/6; median difference 5.0 min; exact Wilcoxon p = 0.031</t>
+          <t xml:space="preserve">  &gt;=10^5 CFU/ml: papGII- n=28 median=22.0 IQR=19.5-27.5 range=14-36 never_crossed=1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4. uidA TTT in mixed vs single-species cultures</t>
+          <t xml:space="preserve">  &gt;=10^5 CFU/ml: Mann-Whitney p = 0.336</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mixed: n=5 median=28.0 IQR=27.0-34.0 range=19-35 never_crossed=0</t>
+          <t>3. papGII vs uidA primer set in papGII-positive urines (paired)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  single: n=33 median=22.0 IQR=18.8-26.2 range=14-36 never_crossed=1</t>
+          <t xml:space="preserve">  papGII primers: n=6 median=17.0 IQR=16.0-18.0 range=13-20 never_crossed=0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5. TTT of reference-positive vs reference-negative samples</t>
+          <t xml:space="preserve">  uidA primers:   n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  uidA positives: n=38 median=22.0 IQR=19.0-28.0 range=14-36 never_crossed=1</t>
+          <t xml:space="preserve">  papGII earlier in 6/6; median difference 5.0 min; exact Wilcoxon p = 0.031</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  uidA negatives crossing: n=153 median=34.0 IQR=32.0-38.0 range=18-40 never_crossed=91; earliest 18 min; crossing after the 30-min threshold: 54</t>
+          <t>4. uidA TTT in mixed vs single-species cultures</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">  papGII positives: n=6 median=17.0 IQR=16.0-18.0 range=13-20 never_crossed=0</t>
+          <t xml:space="preserve">  mixed: n=5 median=28.0 IQR=27.0-34.0 range=19-35 never_crossed=0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  single: n=33 median=22.0 IQR=18.8-26.2 range=14-36 never_crossed=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>5. TTT of reference-positive vs reference-negative samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  uidA positives: n=38 median=22.0 IQR=19.0-28.0 range=14-36 never_crossed=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  uidA negatives crossing: n=153 median=34.0 IQR=32.0-38.0 range=18-40 never_crossed=91; earliest 18 min; crossing after the 30-min threshold: 54</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  papGII positives: n=6 median=17.0 IQR=16.0-18.0 range=13-20 never_crossed=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t xml:space="preserve">  papGII negatives crossing: n=185 median=35.0 IQR=32.0-38.0 range=26-40 never_crossed=112; earliest 26 min; crossing after the 23-min threshold: 73</t>
         </is>

--- a/results/supplement/Supplementary_Tables.xlsx
+++ b/results/supplement/Supplementary_Tables.xlsx
@@ -442,7 +442,7 @@
     <col width="35" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -461,7 +461,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LAMP result: 1 = positive (uidA: &lt;= 30 min and &gt;= 3-fold; papGII: &lt;= 23 min and &gt;= 3-fold); time to threshold empty = fluorescence threshold not reached within 40 min. Bacterial density from semi-quantitative culture of 10 ul (categories &lt;10^4, 10^4, 10^5 and &gt;10^5 CFU/ml). papG alleles: BLASTN vs papG classes I-IV (&gt;= 90% identity, &gt;= 80% coverage); phylogroups: EzClermont.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>LAMP result: 1 = positive (</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">: &lt;= 30 min and &gt;= 3-fold; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">: &lt;= 23 min and &gt;= 3-fold); time to threshold empty = fluorescence threshold not reached within 40 min. Bacterial density from semi-quantitative culture of 10 ul (categories &lt;10^4, 10^4, 10^5 and &gt;10^5 CFU/ml). </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> alleles: BLASTN vs </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> classes I-IV (&gt;= 90% identity, &gt;= 80% coverage); phylogroups: EzClermont.</t>
+          </r>
         </is>
       </c>
     </row>
@@ -489,52 +555,172 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>E. coli by culture (1 = positive)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>E. coli</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> by culture (1 = positive)</t>
+          </r>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>papGII by WGS (1 = positive)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> by WGS (1 = positive)</t>
+          </r>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>papG alleles by WGS</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>papG</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> alleles by WGS</t>
+          </r>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>Phylogroup</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>E. coli</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> phylogroup</t>
+          </r>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>uidA LAMP result</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> LAMP result</t>
+          </r>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>uidA time to threshold (min)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> time to threshold (min)</t>
+          </r>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>papGII LAMP result</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> LAMP result</t>
+          </r>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>papGII time to threshold (min)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> time to threshold (min)</t>
+          </r>
         </is>
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>uidA LAMP correct</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> LAMP correct</t>
+          </r>
         </is>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>papGII LAMP correct</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> LAMP correct</t>
+          </r>
         </is>
       </c>
     </row>
@@ -563,8 +749,6 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -613,16 +797,12 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -659,16 +839,12 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -696,7 +872,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E8" t="n">
@@ -724,7 +907,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -752,7 +934,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Proteus mirabilis, Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Proteus mirabilis</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E9" t="n">
@@ -763,7 +967,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>papGIII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -819,8 +1030,6 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -860,7 +1069,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lactobacillus sp.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Lactobacillus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> sp.</t>
+          </r>
         </is>
       </c>
       <c r="E11" t="n">
@@ -869,8 +1092,6 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>1</v>
       </c>
@@ -919,12 +1140,9 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>0</v>
       </c>
@@ -958,7 +1176,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E13" t="n">
@@ -969,7 +1194,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1025,16 +1257,12 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1062,7 +1290,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1073,7 +1308,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>papGIII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1090,7 +1332,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1127,16 +1368,12 @@
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1164,7 +1401,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1231,12 +1475,9 @@
       <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
         <v>0</v>
       </c>
@@ -1270,7 +1511,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1281,7 +1529,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>papGIV</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIV</t>
+          </r>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1298,7 +1553,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1335,16 +1589,12 @@
       <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1372,7 +1622,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1383,7 +1640,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1430,7 +1694,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1441,7 +1712,29 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>papGII, papGIV</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIV</t>
+          </r>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1488,7 +1781,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1555,16 +1855,12 @@
       <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1601,8 +1897,6 @@
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>1</v>
       </c>
@@ -1612,7 +1906,6 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>no</t>
@@ -1649,16 +1942,12 @@
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1695,16 +1984,12 @@
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1732,7 +2017,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1743,7 +2035,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>papGIV</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIV</t>
+          </r>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1760,7 +2059,6 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1797,16 +2095,12 @@
       <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1834,7 +2128,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1862,7 +2163,6 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1899,16 +2199,12 @@
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1945,16 +2241,12 @@
       <c r="F32" t="n">
         <v>0</v>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1982,7 +2274,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Candida glabrata</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Candida glabrata</t>
+          </r>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1991,12 +2290,9 @@
       <c r="F33" t="n">
         <v>0</v>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -2039,16 +2335,12 @@
       <c r="F34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2076,7 +2368,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2104,7 +2403,6 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2141,16 +2439,12 @@
       <c r="F36" t="n">
         <v>0</v>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2187,12 +2481,9 @@
       <c r="F37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
         <v>0</v>
       </c>
@@ -2235,12 +2526,9 @@
       <c r="F38" t="n">
         <v>0</v>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
         <v>0</v>
       </c>
@@ -2274,7 +2562,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2302,7 +2597,6 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2330,7 +2624,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Actinomyces neuii</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Actinomyces neuii</t>
+          </r>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2339,16 +2640,12 @@
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2385,16 +2682,12 @@
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2431,16 +2724,12 @@
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2477,8 +2766,6 @@
       <c r="F43" t="n">
         <v>0</v>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -2527,8 +2814,6 @@
       <c r="F44" t="n">
         <v>0</v>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>1</v>
       </c>
@@ -2577,8 +2862,6 @@
       <c r="F45" t="n">
         <v>0</v>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -2618,7 +2901,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2685,8 +2975,6 @@
       <c r="F47" t="n">
         <v>0</v>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -2726,7 +3014,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Streptococcus agalactiae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Streptococcus agalactiae</t>
+          </r>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2735,8 +3030,6 @@
       <c r="F48" t="n">
         <v>0</v>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -2776,7 +3069,21 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Lactobacillus sp.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Lactobacillus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> sp.</t>
+          </r>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2785,16 +3092,12 @@
       <c r="F49" t="n">
         <v>0</v>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
         <v>0</v>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2831,8 +3134,6 @@
       <c r="F50" t="n">
         <v>0</v>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -2872,7 +3173,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E51" t="n">
@@ -2900,7 +3208,6 @@
       <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2937,16 +3244,12 @@
       <c r="F52" t="n">
         <v>0</v>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
         <v>0</v>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2983,8 +3286,6 @@
       <c r="F53" t="n">
         <v>0</v>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -3033,16 +3334,12 @@
       <c r="F54" t="n">
         <v>0</v>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
         <v>0</v>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3070,7 +3367,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Candida kefyr</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Candida kefyr</t>
+          </r>
         </is>
       </c>
       <c r="E55" t="n">
@@ -3079,8 +3383,6 @@
       <c r="F55" t="n">
         <v>0</v>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1</v>
       </c>
@@ -3129,8 +3431,6 @@
       <c r="F56" t="n">
         <v>0</v>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -3140,7 +3440,6 @@
       <c r="K56" t="n">
         <v>0</v>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3177,8 +3476,6 @@
       <c r="F57" t="n">
         <v>0</v>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -3227,16 +3524,12 @@
       <c r="F58" t="n">
         <v>0</v>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>0</v>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
         <v>0</v>
       </c>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3264,7 +3557,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Aerococcus viridans</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Aerococcus viridans</t>
+          </r>
         </is>
       </c>
       <c r="E59" t="n">
@@ -3273,16 +3573,12 @@
       <c r="F59" t="n">
         <v>0</v>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>0</v>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3310,7 +3606,21 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lactobacillus sp.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Lactobacillus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> sp.</t>
+          </r>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3319,16 +3629,12 @@
       <c r="F60" t="n">
         <v>0</v>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="n">
         <v>0</v>
       </c>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3356,7 +3662,21 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Streptococcus spp.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Streptococcus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> spp.</t>
+          </r>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3365,16 +3685,12 @@
       <c r="F61" t="n">
         <v>0</v>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
         <v>0</v>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3411,8 +3727,6 @@
       <c r="F62" t="n">
         <v>0</v>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -3422,7 +3736,6 @@
       <c r="K62" t="n">
         <v>0</v>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3459,16 +3772,12 @@
       <c r="F63" t="n">
         <v>0</v>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="n">
         <v>0</v>
       </c>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3496,7 +3805,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Enterococcus faecium</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Enterococcus faecium</t>
+          </r>
         </is>
       </c>
       <c r="E64" t="n">
@@ -3505,8 +3821,6 @@
       <c r="F64" t="n">
         <v>0</v>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -3516,7 +3830,6 @@
       <c r="K64" t="n">
         <v>0</v>
       </c>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3553,8 +3866,6 @@
       <c r="F65" t="n">
         <v>0</v>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -3594,7 +3905,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3605,7 +3923,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>papGIII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3652,7 +3977,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E67" t="n">
@@ -3680,7 +4012,6 @@
       <c r="K67" t="n">
         <v>0</v>
       </c>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3708,7 +4039,29 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Enterococcus faecalis, Morganella morganii</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Enterococcus faecalis</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Morganella morganii</t>
+          </r>
         </is>
       </c>
       <c r="E68" t="n">
@@ -3717,16 +4070,12 @@
       <c r="F68" t="n">
         <v>0</v>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>0</v>
       </c>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
         <v>0</v>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3754,7 +4103,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E69" t="n">
@@ -3765,7 +4121,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>papGIII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3782,7 +4145,6 @@
       <c r="K69" t="n">
         <v>0</v>
       </c>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3819,8 +4181,6 @@
       <c r="F70" t="n">
         <v>0</v>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -3869,16 +4229,12 @@
       <c r="F71" t="n">
         <v>0</v>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="n">
         <v>0</v>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3906,7 +4262,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Enterococcus faecalis</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Enterococcus faecalis</t>
+          </r>
         </is>
       </c>
       <c r="E72" t="n">
@@ -3915,8 +4278,6 @@
       <c r="F72" t="n">
         <v>0</v>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -3926,7 +4287,6 @@
       <c r="K72" t="n">
         <v>0</v>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3954,7 +4314,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Klebsiella oxytoca</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella oxytoca</t>
+          </r>
         </is>
       </c>
       <c r="E73" t="n">
@@ -3963,16 +4330,12 @@
       <c r="F73" t="n">
         <v>0</v>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>0</v>
       </c>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
         <v>0</v>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4000,7 +4363,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Staphylococcus borealis</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Staphylococcus borealis</t>
+          </r>
         </is>
       </c>
       <c r="E74" t="n">
@@ -4009,16 +4379,12 @@
       <c r="F74" t="n">
         <v>0</v>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
         <v>0</v>
       </c>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
         <v>0</v>
       </c>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4046,7 +4412,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella pneumoniae</t>
+          </r>
         </is>
       </c>
       <c r="E75" t="n">
@@ -4055,16 +4428,12 @@
       <c r="F75" t="n">
         <v>0</v>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
         <v>0</v>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4092,7 +4461,44 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Staphylococcus xylosus, Escherichia coli, Pantoea calida</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Staphylococcus xylosus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Pantoea calida</t>
+          </r>
         </is>
       </c>
       <c r="E76" t="n">
@@ -4150,7 +4556,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella pneumoniae</t>
+          </r>
         </is>
       </c>
       <c r="E77" t="n">
@@ -4159,8 +4572,6 @@
       <c r="F77" t="n">
         <v>0</v>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -4200,7 +4611,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E78" t="n">
@@ -4211,7 +4629,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>papGIII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4228,7 +4653,6 @@
       <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4265,12 +4689,9 @@
       <c r="F79" t="n">
         <v>0</v>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
         <v>0</v>
       </c>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
         <v>0</v>
       </c>
@@ -4313,8 +4734,6 @@
       <c r="F80" t="n">
         <v>0</v>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -4324,7 +4743,6 @@
       <c r="K80" t="n">
         <v>0</v>
       </c>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4361,8 +4779,6 @@
       <c r="F81" t="n">
         <v>0</v>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -4402,7 +4818,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella pneumoniae</t>
+          </r>
         </is>
       </c>
       <c r="E82" t="n">
@@ -4411,16 +4834,12 @@
       <c r="F82" t="n">
         <v>0</v>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
         <v>0</v>
       </c>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
         <v>0</v>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4448,7 +4867,29 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae, Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella pneumoniae</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E83" t="n">
@@ -4515,8 +4956,6 @@
       <c r="F84" t="n">
         <v>0</v>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -4565,8 +5004,6 @@
       <c r="F85" t="n">
         <v>0</v>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -4576,7 +5013,6 @@
       <c r="K85" t="n">
         <v>0</v>
       </c>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4604,7 +5040,21 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lactobacillus sp.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Lactobacillus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> sp.</t>
+          </r>
         </is>
       </c>
       <c r="E86" t="n">
@@ -4613,12 +5063,9 @@
       <c r="F86" t="n">
         <v>0</v>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
         <v>0</v>
       </c>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
         <v>0</v>
       </c>
@@ -4661,8 +5108,6 @@
       <c r="F87" t="n">
         <v>0</v>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -4711,8 +5156,6 @@
       <c r="F88" t="n">
         <v>0</v>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -4761,8 +5204,6 @@
       <c r="F89" t="n">
         <v>0</v>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -4802,7 +5243,14 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E90" t="n">
@@ -4830,7 +5278,6 @@
       <c r="K90" t="n">
         <v>0</v>
       </c>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4867,8 +5314,6 @@
       <c r="F91" t="n">
         <v>0</v>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -4917,8 +5362,6 @@
       <c r="F92" t="n">
         <v>0</v>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -4958,7 +5401,21 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Lactobacillus sp.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Lactobacillus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> sp.</t>
+          </r>
         </is>
       </c>
       <c r="E93" t="n">
@@ -4967,8 +5424,6 @@
       <c r="F93" t="n">
         <v>0</v>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -5017,16 +5472,12 @@
       <c r="F94" t="n">
         <v>0</v>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
         <v>0</v>
       </c>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
         <v>0</v>
       </c>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5063,12 +5514,9 @@
       <c r="F95" t="n">
         <v>0</v>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
         <v>0</v>
       </c>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
         <v>0</v>
       </c>
@@ -5111,8 +5559,6 @@
       <c r="F96" t="n">
         <v>0</v>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -5122,7 +5568,6 @@
       <c r="K96" t="n">
         <v>0</v>
       </c>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5150,7 +5595,14 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E97" t="n">
@@ -5208,7 +5660,21 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Lactobacillus sp.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Lactobacillus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> sp.</t>
+          </r>
         </is>
       </c>
       <c r="E98" t="n">
@@ -5217,8 +5683,6 @@
       <c r="F98" t="n">
         <v>0</v>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -5267,8 +5731,6 @@
       <c r="F99" t="n">
         <v>0</v>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -5317,16 +5779,12 @@
       <c r="F100" t="n">
         <v>0</v>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
         <v>0</v>
       </c>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
         <v>0</v>
       </c>
-      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5363,16 +5821,12 @@
       <c r="F101" t="n">
         <v>0</v>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
         <v>0</v>
       </c>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
         <v>0</v>
       </c>
-      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5400,7 +5854,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E102" t="n">
@@ -5411,7 +5872,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>papGIII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5428,7 +5896,6 @@
       <c r="K102" t="n">
         <v>0</v>
       </c>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5465,8 +5932,6 @@
       <c r="F103" t="n">
         <v>0</v>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
         <v>0</v>
       </c>
@@ -5515,16 +5980,12 @@
       <c r="F104" t="n">
         <v>0</v>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
         <v>0</v>
       </c>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
         <v>0</v>
       </c>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5561,8 +6022,6 @@
       <c r="F105" t="n">
         <v>0</v>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
         <v>0</v>
       </c>
@@ -5572,7 +6031,6 @@
       <c r="K105" t="n">
         <v>0</v>
       </c>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5609,12 +6067,9 @@
       <c r="F106" t="n">
         <v>0</v>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
         <v>0</v>
       </c>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
         <v>0</v>
       </c>
@@ -5648,7 +6103,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Enterococcus faecalis</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Enterococcus faecalis</t>
+          </r>
         </is>
       </c>
       <c r="E107" t="n">
@@ -5657,8 +6119,6 @@
       <c r="F107" t="n">
         <v>0</v>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
         <v>1</v>
       </c>
@@ -5698,7 +6158,14 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Proteus mirabilis</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Proteus mirabilis</t>
+          </r>
         </is>
       </c>
       <c r="E108" t="n">
@@ -5707,8 +6174,6 @@
       <c r="F108" t="n">
         <v>0</v>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
         <v>0</v>
       </c>
@@ -5757,8 +6222,6 @@
       <c r="F109" t="n">
         <v>0</v>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
         <v>0</v>
       </c>
@@ -5807,16 +6270,12 @@
       <c r="F110" t="n">
         <v>0</v>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
         <v>0</v>
       </c>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
         <v>0</v>
       </c>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5844,7 +6303,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E111" t="n">
@@ -5855,7 +6321,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>papGIV</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIV</t>
+          </r>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5866,11 +6339,9 @@
       <c r="I111" t="n">
         <v>0</v>
       </c>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="n">
         <v>0</v>
       </c>
-      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>no</t>
@@ -5907,16 +6378,12 @@
       <c r="F112" t="n">
         <v>0</v>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
         <v>0</v>
       </c>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="n">
         <v>0</v>
       </c>
-      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5944,7 +6411,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Klebsiella oxytoca</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella oxytoca</t>
+          </r>
         </is>
       </c>
       <c r="E113" t="n">
@@ -5953,8 +6427,6 @@
       <c r="F113" t="n">
         <v>0</v>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
         <v>0</v>
       </c>
@@ -5964,7 +6436,6 @@
       <c r="K113" t="n">
         <v>0</v>
       </c>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6001,8 +6472,6 @@
       <c r="F114" t="n">
         <v>0</v>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
         <v>1</v>
       </c>
@@ -6042,7 +6511,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E115" t="n">
@@ -6053,7 +6529,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>papGIII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6100,7 +6583,14 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E116" t="n">
@@ -6111,7 +6601,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6167,16 +6664,12 @@
       <c r="F117" t="n">
         <v>0</v>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
         <v>0</v>
       </c>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
         <v>0</v>
       </c>
-      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6213,8 +6706,6 @@
       <c r="F118" t="n">
         <v>0</v>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
         <v>0</v>
       </c>
@@ -6263,8 +6754,6 @@
       <c r="F119" t="n">
         <v>0</v>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
         <v>0</v>
       </c>
@@ -6313,12 +6802,9 @@
       <c r="F120" t="n">
         <v>0</v>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
         <v>0</v>
       </c>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
         <v>0</v>
       </c>
@@ -6361,8 +6847,6 @@
       <c r="F121" t="n">
         <v>0</v>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
         <v>0</v>
       </c>
@@ -6372,7 +6856,6 @@
       <c r="K121" t="n">
         <v>0</v>
       </c>
-      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6409,8 +6892,6 @@
       <c r="F122" t="n">
         <v>0</v>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
         <v>1</v>
       </c>
@@ -6459,8 +6940,6 @@
       <c r="F123" t="n">
         <v>0</v>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
         <v>0</v>
       </c>
@@ -6509,16 +6988,12 @@
       <c r="F124" t="n">
         <v>0</v>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
         <v>0</v>
       </c>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
         <v>0</v>
       </c>
-      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6555,12 +7030,9 @@
       <c r="F125" t="n">
         <v>0</v>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
         <v>0</v>
       </c>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="n">
         <v>0</v>
       </c>
@@ -6603,16 +7075,12 @@
       <c r="F126" t="n">
         <v>0</v>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
         <v>0</v>
       </c>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="n">
         <v>0</v>
       </c>
-      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6640,7 +7108,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Gardnerella vaginalis, Streptococcus anginosus</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Gardnerella vaginalis</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Streptococcus anginosus</t>
+          </r>
         </is>
       </c>
       <c r="E127" t="n">
@@ -6649,16 +7139,12 @@
       <c r="F127" t="n">
         <v>0</v>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
         <v>0</v>
       </c>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
         <v>0</v>
       </c>
-      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6686,7 +7172,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E128" t="n">
@@ -6697,7 +7190,14 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>papGIII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6714,7 +7214,6 @@
       <c r="K128" t="n">
         <v>0</v>
       </c>
-      <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6742,7 +7241,14 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella pneumoniae</t>
+          </r>
         </is>
       </c>
       <c r="E129" t="n">
@@ -6751,8 +7257,6 @@
       <c r="F129" t="n">
         <v>0</v>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
         <v>1</v>
       </c>
@@ -6762,7 +7266,6 @@
       <c r="K129" t="n">
         <v>0</v>
       </c>
-      <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
           <t>no</t>
@@ -6799,8 +7302,6 @@
       <c r="F130" t="n">
         <v>0</v>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
         <v>0</v>
       </c>
@@ -6810,7 +7311,6 @@
       <c r="K130" t="n">
         <v>0</v>
       </c>
-      <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6847,12 +7347,9 @@
       <c r="F131" t="n">
         <v>0</v>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
         <v>0</v>
       </c>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="n">
         <v>0</v>
       </c>
@@ -6895,16 +7392,12 @@
       <c r="F132" t="n">
         <v>0</v>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
         <v>0</v>
       </c>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="n">
         <v>0</v>
       </c>
-      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6941,8 +7434,6 @@
       <c r="F133" t="n">
         <v>0</v>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
         <v>0</v>
       </c>
@@ -6991,16 +7482,12 @@
       <c r="F134" t="n">
         <v>0</v>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
         <v>0</v>
       </c>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="n">
         <v>0</v>
       </c>
-      <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7028,7 +7515,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Klebsiella oxytoca</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella oxytoca</t>
+          </r>
         </is>
       </c>
       <c r="E135" t="n">
@@ -7037,16 +7531,12 @@
       <c r="F135" t="n">
         <v>0</v>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
         <v>0</v>
       </c>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="n">
         <v>0</v>
       </c>
-      <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7083,16 +7573,12 @@
       <c r="F136" t="n">
         <v>0</v>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
         <v>0</v>
       </c>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="n">
         <v>0</v>
       </c>
-      <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7129,16 +7615,12 @@
       <c r="F137" t="n">
         <v>0</v>
       </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
         <v>0</v>
       </c>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="n">
         <v>0</v>
       </c>
-      <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7166,7 +7648,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Proteus mirabilis</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Proteus mirabilis</t>
+          </r>
         </is>
       </c>
       <c r="E138" t="n">
@@ -7175,8 +7664,6 @@
       <c r="F138" t="n">
         <v>0</v>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="n">
         <v>0</v>
       </c>
@@ -7225,16 +7712,12 @@
       <c r="F139" t="n">
         <v>0</v>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
         <v>0</v>
       </c>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="n">
         <v>0</v>
       </c>
-      <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7271,16 +7754,12 @@
       <c r="F140" t="n">
         <v>0</v>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
         <v>0</v>
       </c>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="n">
         <v>0</v>
       </c>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7317,16 +7796,12 @@
       <c r="F141" t="n">
         <v>0</v>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
         <v>0</v>
       </c>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="n">
         <v>0</v>
       </c>
-      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7363,8 +7838,6 @@
       <c r="F142" t="n">
         <v>0</v>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
         <v>0</v>
       </c>
@@ -7404,7 +7877,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E143" t="n">
@@ -7432,7 +7912,6 @@
       <c r="K143" t="n">
         <v>0</v>
       </c>
-      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7469,16 +7948,12 @@
       <c r="F144" t="n">
         <v>0</v>
       </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
         <v>0</v>
       </c>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="n">
         <v>0</v>
       </c>
-      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7515,16 +7990,12 @@
       <c r="F145" t="n">
         <v>0</v>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
         <v>0</v>
       </c>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="n">
         <v>0</v>
       </c>
-      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7561,16 +8032,12 @@
       <c r="F146" t="n">
         <v>0</v>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
         <v>0</v>
       </c>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="n">
         <v>0</v>
       </c>
-      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7607,16 +8074,12 @@
       <c r="F147" t="n">
         <v>0</v>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
         <v>0</v>
       </c>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="n">
         <v>0</v>
       </c>
-      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7653,16 +8116,12 @@
       <c r="F148" t="n">
         <v>0</v>
       </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
         <v>0</v>
       </c>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="n">
         <v>0</v>
       </c>
-      <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7690,7 +8149,14 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Candida albicans</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Candida albicans</t>
+          </r>
         </is>
       </c>
       <c r="E149" t="n">
@@ -7699,8 +8165,6 @@
       <c r="F149" t="n">
         <v>0</v>
       </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
         <v>0</v>
       </c>
@@ -7710,7 +8174,6 @@
       <c r="K149" t="n">
         <v>0</v>
       </c>
-      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7747,16 +8210,12 @@
       <c r="F150" t="n">
         <v>0</v>
       </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
         <v>0</v>
       </c>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="n">
         <v>0</v>
       </c>
-      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7784,7 +8243,14 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Staphylococcus epidermidis</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Staphylococcus epidermidis</t>
+          </r>
         </is>
       </c>
       <c r="E151" t="n">
@@ -7793,16 +8259,12 @@
       <c r="F151" t="n">
         <v>0</v>
       </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
         <v>0</v>
       </c>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="n">
         <v>0</v>
       </c>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7839,8 +8301,6 @@
       <c r="F152" t="n">
         <v>0</v>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
         <v>0</v>
       </c>
@@ -7850,7 +8310,6 @@
       <c r="K152" t="n">
         <v>0</v>
       </c>
-      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7878,7 +8337,14 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Klebsiella oxytoca</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella oxytoca</t>
+          </r>
         </is>
       </c>
       <c r="E153" t="n">
@@ -7887,16 +8353,12 @@
       <c r="F153" t="n">
         <v>0</v>
       </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
         <v>0</v>
       </c>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="n">
         <v>0</v>
       </c>
-      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7924,7 +8386,21 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Streptococcus spp.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Streptococcus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> spp.</t>
+          </r>
         </is>
       </c>
       <c r="E154" t="n">
@@ -7933,16 +8409,12 @@
       <c r="F154" t="n">
         <v>0</v>
       </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
         <v>0</v>
       </c>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="n">
         <v>0</v>
       </c>
-      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7970,7 +8442,29 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae, Enterobacter cloacae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella pneumoniae</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Enterobacter cloacae</t>
+          </r>
         </is>
       </c>
       <c r="E155" t="n">
@@ -7979,16 +8473,12 @@
       <c r="F155" t="n">
         <v>0</v>
       </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>0</v>
       </c>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="n">
         <v>0</v>
       </c>
-      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8016,7 +8506,21 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Lactobacillus sp.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Lactobacillus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> sp.</t>
+          </r>
         </is>
       </c>
       <c r="E156" t="n">
@@ -8025,16 +8529,12 @@
       <c r="F156" t="n">
         <v>0</v>
       </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
         <v>0</v>
       </c>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="n">
         <v>0</v>
       </c>
-      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8062,7 +8562,14 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E157" t="n">
@@ -8090,7 +8597,6 @@
       <c r="K157" t="n">
         <v>0</v>
       </c>
-      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8118,7 +8624,14 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E158" t="n">
@@ -8146,7 +8659,6 @@
       <c r="K158" t="n">
         <v>0</v>
       </c>
-      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8174,7 +8686,29 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Escherichia coli, Aerococcus urinae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Aerococcus urinae</t>
+          </r>
         </is>
       </c>
       <c r="E159" t="n">
@@ -8202,7 +8736,6 @@
       <c r="K159" t="n">
         <v>0</v>
       </c>
-      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
           <t>no</t>
@@ -8230,7 +8763,29 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Enterococcus faecalis, Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Enterococcus faecalis</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E160" t="n">
@@ -8258,7 +8813,6 @@
       <c r="K160" t="n">
         <v>0</v>
       </c>
-      <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
           <t>no</t>
@@ -8286,7 +8840,14 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E161" t="n">
@@ -8297,7 +8858,14 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>papGIII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8353,8 +8921,6 @@
       <c r="F162" t="n">
         <v>0</v>
       </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
         <v>0</v>
       </c>
@@ -8403,16 +8969,12 @@
       <c r="F163" t="n">
         <v>0</v>
       </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
         <v>0</v>
       </c>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="n">
         <v>0</v>
       </c>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8449,8 +9011,6 @@
       <c r="F164" t="n">
         <v>0</v>
       </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>0</v>
       </c>
@@ -8499,8 +9059,6 @@
       <c r="F165" t="n">
         <v>0</v>
       </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>0</v>
       </c>
@@ -8510,7 +9068,6 @@
       <c r="K165" t="n">
         <v>0</v>
       </c>
-      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8547,16 +9104,12 @@
       <c r="F166" t="n">
         <v>0</v>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>0</v>
       </c>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="n">
         <v>0</v>
       </c>
-      <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8593,16 +9146,12 @@
       <c r="F167" t="n">
         <v>0</v>
       </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>0</v>
       </c>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="n">
         <v>0</v>
       </c>
-      <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8630,7 +9179,14 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Lactobacillus gasseri</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Lactobacillus gasseri</t>
+          </r>
         </is>
       </c>
       <c r="E168" t="n">
@@ -8639,8 +9195,6 @@
       <c r="F168" t="n">
         <v>0</v>
       </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>0</v>
       </c>
@@ -8689,8 +9243,6 @@
       <c r="F169" t="n">
         <v>0</v>
       </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>0</v>
       </c>
@@ -8739,8 +9291,6 @@
       <c r="F170" t="n">
         <v>0</v>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>0</v>
       </c>
@@ -8750,7 +9300,6 @@
       <c r="K170" t="n">
         <v>0</v>
       </c>
-      <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8787,16 +9336,12 @@
       <c r="F171" t="n">
         <v>0</v>
       </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>0</v>
       </c>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="n">
         <v>0</v>
       </c>
-      <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8824,7 +9369,14 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Candida albicans</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Candida albicans</t>
+          </r>
         </is>
       </c>
       <c r="E172" t="n">
@@ -8833,16 +9385,12 @@
       <c r="F172" t="n">
         <v>0</v>
       </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>0</v>
       </c>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="n">
         <v>0</v>
       </c>
-      <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8879,8 +9427,6 @@
       <c r="F173" t="n">
         <v>0</v>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>0</v>
       </c>
@@ -8929,8 +9475,6 @@
       <c r="F174" t="n">
         <v>0</v>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>0</v>
       </c>
@@ -8940,7 +9484,6 @@
       <c r="K174" t="n">
         <v>0</v>
       </c>
-      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8977,12 +9520,9 @@
       <c r="F175" t="n">
         <v>0</v>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0</v>
       </c>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="n">
         <v>0</v>
       </c>
@@ -9016,7 +9556,14 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E176" t="n">
@@ -9027,7 +9574,29 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>papGII, papGIV</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIV</t>
+          </r>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -9074,7 +9643,14 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E177" t="n">
@@ -9141,8 +9717,6 @@
       <c r="F178" t="n">
         <v>0</v>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0</v>
       </c>
@@ -9191,8 +9765,6 @@
       <c r="F179" t="n">
         <v>0</v>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>0</v>
       </c>
@@ -9241,16 +9813,12 @@
       <c r="F180" t="n">
         <v>0</v>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>0</v>
       </c>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="n">
         <v>0</v>
       </c>
-      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9287,12 +9855,9 @@
       <c r="F181" t="n">
         <v>0</v>
       </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>0</v>
       </c>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="n">
         <v>0</v>
       </c>
@@ -9335,12 +9900,9 @@
       <c r="F182" t="n">
         <v>0</v>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
         <v>0</v>
       </c>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="n">
         <v>0</v>
       </c>
@@ -9383,16 +9945,12 @@
       <c r="F183" t="n">
         <v>0</v>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
         <v>0</v>
       </c>
-      <c r="J183" t="inlineStr"/>
       <c r="K183" t="n">
         <v>0</v>
       </c>
-      <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9429,16 +9987,12 @@
       <c r="F184" t="n">
         <v>0</v>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>0</v>
       </c>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="n">
         <v>0</v>
       </c>
-      <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9466,7 +10020,14 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E185" t="n">
@@ -9477,7 +10038,14 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>papGIV</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIV</t>
+          </r>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -9494,7 +10062,6 @@
       <c r="K185" t="n">
         <v>0</v>
       </c>
-      <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9522,7 +10089,14 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E186" t="n">
@@ -9533,7 +10107,14 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9580,7 +10161,14 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Staphylococcus lugdunensis</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Staphylococcus lugdunensis</t>
+          </r>
         </is>
       </c>
       <c r="E187" t="n">
@@ -9589,16 +10177,12 @@
       <c r="F187" t="n">
         <v>0</v>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
         <v>0</v>
       </c>
-      <c r="J187" t="inlineStr"/>
       <c r="K187" t="n">
         <v>0</v>
       </c>
-      <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9635,16 +10219,12 @@
       <c r="F188" t="n">
         <v>0</v>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
         <v>0</v>
       </c>
-      <c r="J188" t="inlineStr"/>
       <c r="K188" t="n">
         <v>0</v>
       </c>
-      <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9681,16 +10261,12 @@
       <c r="F189" t="n">
         <v>0</v>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
         <v>0</v>
       </c>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="n">
         <v>0</v>
       </c>
-      <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9727,16 +10303,12 @@
       <c r="F190" t="n">
         <v>0</v>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
         <v>0</v>
       </c>
-      <c r="J190" t="inlineStr"/>
       <c r="K190" t="n">
         <v>0</v>
       </c>
-      <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9773,16 +10345,12 @@
       <c r="F191" t="n">
         <v>0</v>
       </c>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
         <v>0</v>
       </c>
-      <c r="J191" t="inlineStr"/>
       <c r="K191" t="n">
         <v>0</v>
       </c>
-      <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9819,12 +10387,9 @@
       <c r="F192" t="n">
         <v>0</v>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="n">
         <v>0</v>
       </c>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="n">
         <v>0</v>
       </c>
@@ -9867,16 +10432,12 @@
       <c r="F193" t="n">
         <v>0</v>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
         <v>0</v>
       </c>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="n">
         <v>0</v>
       </c>
-      <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9913,12 +10474,9 @@
       <c r="F194" t="n">
         <v>0</v>
       </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
         <v>0</v>
       </c>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="n">
         <v>0</v>
       </c>
@@ -9952,7 +10510,14 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella pneumoniae</t>
+          </r>
         </is>
       </c>
       <c r="E195" t="n">
@@ -9961,12 +10526,9 @@
       <c r="F195" t="n">
         <v>0</v>
       </c>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
         <v>0</v>
       </c>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="n">
         <v>0</v>
       </c>
@@ -10016,7 +10578,28 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Supplementary Table 2. uidA: the ten highest-ranking results of the threshold search by Youden's index (191 samples).</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Supplementary Table 2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>: the ten highest-ranking results of the threshold search by Youden's index (191 samples).</t>
+          </r>
         </is>
       </c>
     </row>
@@ -10719,7 +11302,28 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Supplementary Table 3. papGII: diagnostic metrics at different time thresholds (fluorescence threshold &gt;= 3-fold change; 191 samples).</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Supplementary Table 3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>: diagnostic metrics at different time thresholds (fluorescence threshold &gt;= 3-fold change; 191 samples).</t>
+          </r>
         </is>
       </c>
     </row>
@@ -11245,7 +11849,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>uidA: per Clermont phylogroup (genomes with the target region present). papGII: per PapG class (best-matching papG locus of each genome), with minimum and maximum.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">: per Clermont phylogroup (genomes with the target region present). </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">: per PapG class (best-matching </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> locus of each genome), with minimum and maximum.</t>
+          </r>
         </is>
       </c>
     </row>
@@ -12438,7 +13086,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12479,7 +13134,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12520,7 +13182,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12561,7 +13230,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12595,12 +13271,18 @@
       <c r="J54" t="n">
         <v>0</v>
       </c>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12634,12 +13316,18 @@
       <c r="J55" t="n">
         <v>0</v>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -12680,7 +13368,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12721,7 +13416,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12762,7 +13464,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12803,7 +13512,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12844,7 +13560,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12885,7 +13608,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12919,12 +13649,18 @@
       <c r="J62" t="n">
         <v>0</v>
       </c>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12958,12 +13694,18 @@
       <c r="J63" t="n">
         <v>0</v>
       </c>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13004,7 +13746,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -13045,7 +13794,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13140,7 +13896,51 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>papGII (alone or with papGIII/papGIV)</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> (alone or with </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIV</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="B70" t="n">
@@ -13174,7 +13974,21 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>papGIII only</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> only</t>
+          </r>
         </is>
       </c>
       <c r="B71" t="n">
@@ -13208,7 +14022,21 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>papGIV only</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGIV</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> only</t>
+          </r>
         </is>
       </c>
       <c r="B72" t="n">
@@ -13242,7 +14070,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>no papG allele</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">no </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papG</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> allele</t>
+          </r>
         </is>
       </c>
       <c r="B73" t="n">
@@ -13822,7 +14671,43 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Supplementary Table 6. Time to threshold of the 38 E. coli-positive urine samples by bacterial density, papGII status and primer set.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Supplementary Table 6. Time to threshold of the 38 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>E. coli</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">-positive urine samples by bacterial density, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> status and primer set.</t>
+          </r>
         </is>
       </c>
     </row>
@@ -13857,17 +14742,53 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>papGII by WGS</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> by WGS</t>
+          </r>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>uidA time to threshold (min)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> time to threshold (min)</t>
+          </r>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>papGII time to threshold (min)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <i val="1"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve"> time to threshold (min)</t>
+          </r>
         </is>
       </c>
     </row>
@@ -13884,7 +14805,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D5" t="n">
@@ -13913,7 +14841,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D6" t="n">
@@ -13942,7 +14877,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D7" t="n">
@@ -13971,7 +14913,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D8" t="n">
@@ -14000,7 +14949,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D9" t="n">
@@ -14029,7 +14985,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D10" t="n">
@@ -14041,7 +15004,6 @@
       <c r="F10" t="n">
         <v>18</v>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14056,7 +15018,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D11" t="n">
@@ -14068,7 +15037,6 @@
       <c r="F11" t="n">
         <v>18</v>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14083,7 +15051,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D12" t="n">
@@ -14095,7 +15070,6 @@
       <c r="F12" t="n">
         <v>18</v>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14110,7 +15084,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Proteus mirabilis, Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Proteus mirabilis</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D13" t="n">
@@ -14139,7 +15135,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D14" t="n">
@@ -14151,7 +15154,6 @@
       <c r="F14" t="n">
         <v>19</v>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14166,7 +15168,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D15" t="n">
@@ -14178,7 +15187,6 @@
       <c r="F15" t="n">
         <v>20</v>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14193,7 +15201,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D16" t="n">
@@ -14222,7 +15237,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D17" t="n">
@@ -14234,7 +15256,6 @@
       <c r="F17" t="n">
         <v>21</v>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14249,7 +15270,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D18" t="n">
@@ -14278,7 +15306,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D19" t="n">
@@ -14307,7 +15342,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D20" t="n">
@@ -14336,7 +15378,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D21" t="n">
@@ -14348,7 +15397,6 @@
       <c r="F21" t="n">
         <v>22</v>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14363,7 +15411,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D22" t="n">
@@ -14375,7 +15430,6 @@
       <c r="F22" t="n">
         <v>22</v>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14390,7 +15444,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D23" t="n">
@@ -14402,7 +15463,6 @@
       <c r="F23" t="n">
         <v>22</v>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14417,7 +15477,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D24" t="n">
@@ -14429,7 +15496,6 @@
       <c r="F24" t="n">
         <v>24</v>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14444,7 +15510,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D25" t="n">
@@ -14456,7 +15529,6 @@
       <c r="F25" t="n">
         <v>25</v>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14471,7 +15543,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D26" t="n">
@@ -14500,7 +15579,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D27" t="n">
@@ -14512,7 +15598,6 @@
       <c r="F27" t="n">
         <v>26</v>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14527,7 +15612,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D28" t="n">
@@ -14556,7 +15648,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D29" t="n">
@@ -14568,7 +15667,6 @@
       <c r="F29" t="n">
         <v>26</v>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14583,7 +15681,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D30" t="n">
@@ -14595,7 +15700,6 @@
       <c r="F30" t="n">
         <v>27</v>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14610,7 +15714,44 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Staphylococcus xylosus, Escherichia coli, Pantoea calida</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Staphylococcus xylosus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Pantoea calida</t>
+          </r>
         </is>
       </c>
       <c r="D31" t="n">
@@ -14639,7 +15780,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D32" t="n">
@@ -14651,7 +15799,6 @@
       <c r="F32" t="n">
         <v>28</v>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14666,7 +15813,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D33" t="n">
@@ -14678,7 +15832,6 @@
       <c r="F33" t="n">
         <v>28</v>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -14693,7 +15846,29 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae, Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella pneumoniae</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D34" t="n">
@@ -14722,7 +15897,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D35" t="n">
@@ -14734,7 +15916,6 @@
       <c r="F35" t="n">
         <v>29</v>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14749,7 +15930,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D36" t="n">
@@ -14778,7 +15966,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D37" t="n">
@@ -14790,7 +15985,6 @@
       <c r="F37" t="n">
         <v>30</v>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -14805,7 +15999,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D38" t="n">
@@ -14834,7 +16035,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Enterococcus faecalis, Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Enterococcus faecalis</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D39" t="n">
@@ -14846,7 +16069,6 @@
       <c r="F39" t="n">
         <v>34</v>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14861,7 +16083,29 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Escherichia coli, Aerococcus urinae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Aerococcus urinae</t>
+          </r>
         </is>
       </c>
       <c r="D40" t="n">
@@ -14873,7 +16117,6 @@
       <c r="F40" t="n">
         <v>35</v>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14888,7 +16131,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D41" t="n">
@@ -14917,7 +16167,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="D42" t="n">
@@ -14926,8 +16183,6 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43"/>
     <row r="44"/>
@@ -14942,7 +16197,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1. uidA TTT by bacterial load (E. coli culture-positive urines)</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> TTT by bacterial load (</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>E. coli</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> culture-positive urines)</t>
+          </r>
         </is>
       </c>
     </row>
@@ -14970,21 +16261,84 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  category 10^4: n=4 median=28.5 IQR=25.0-29.2 range=16-30 never_crossed=0; papGII-positive: 0</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">  category 10^4: n=4 median=28.5 IQR=25.0-29.2 range=16-30 never_crossed=0; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-positive: 0</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  category 10^5: n=7 median=27.5 IQR=26.2-29.5 range=21-33 never_crossed=1; papGII-positive: 1</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">  category 10^5: n=7 median=27.5 IQR=26.2-29.5 range=21-33 never_crossed=1; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-positive: 1</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  category &gt;10^5: n=27 median=21.0 IQR=18.5-26.0 range=14-36 never_crossed=0; papGII-positive: 5</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">  category &gt;10^5: n=27 median=21.0 IQR=18.5-26.0 range=14-36 never_crossed=0; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-positive: 5</t>
+          </r>
         </is>
       </c>
     </row>
@@ -14998,28 +16352,142 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  within &gt;10^5 CFU/ml: papGII+ n=5 median=21.0 IQR=18.0-26.0 range=18-26 never_crossed=0 vs papGII- n=22 median=21.5 IQR=19.0-25.8 range=14-36 never_crossed=0; Mann-Whitney p = 0.729</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">  within &gt;10^5 CFU/ml: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">+ n=5 median=21.0 IQR=18.0-26.0 range=18-26 never_crossed=0 vs </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>- n=22 median=21.5 IQR=19.0-25.8 range=14-36 never_crossed=0; Mann-Whitney p = 0.729</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2. uidA TTT by papGII status</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> TTT by </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> status</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  all loads: papGII+ n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">  all loads: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>+ n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  all loads: papGII- n=32 median=24.0 IQR=19.5-28.0 range=14-36 never_crossed=1</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">  all loads: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>- n=32 median=24.0 IQR=19.5-28.0 range=14-36 never_crossed=1</t>
+          </r>
         </is>
       </c>
     </row>
@@ -15033,14 +16501,56 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;=10^5 CFU/ml: papGII+ n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">  &gt;=10^5 CFU/ml: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>+ n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;=10^5 CFU/ml: papGII- n=28 median=22.0 IQR=19.5-27.5 range=14-36 never_crossed=1</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">  &gt;=10^5 CFU/ml: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>- n=28 median=22.0 IQR=19.5-27.5 range=14-36 never_crossed=1</t>
+          </r>
         </is>
       </c>
     </row>
@@ -15054,35 +16564,170 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3. papGII vs uidA primer set in papGII-positive urines (paired)</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> vs </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> primer set in </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-positive urines (paired)</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  papGII primers: n=6 median=17.0 IQR=16.0-18.0 range=13-20 never_crossed=0</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> primers: n=6 median=17.0 IQR=16.0-18.0 range=13-20 never_crossed=0</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  uidA primers:   n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> primers:   n=6 median=21.0 IQR=18.8-24.8 range=18-26 never_crossed=0</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  papGII earlier in 6/6; median difference 5.0 min; exact Wilcoxon p = 0.031</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> earlier in 6/6; median difference 5.0 min; exact Wilcoxon p = 0.031</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4. uidA TTT in mixed vs single-species cultures</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> TTT in mixed vs single-species cultures</t>
+          </r>
         </is>
       </c>
     </row>
@@ -15110,28 +16755,112 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  uidA positives: n=38 median=22.0 IQR=19.0-28.0 range=14-36 never_crossed=1</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> positives: n=38 median=22.0 IQR=19.0-28.0 range=14-36 never_crossed=1</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  uidA negatives crossing: n=153 median=34.0 IQR=32.0-38.0 range=18-40 never_crossed=91; earliest 18 min; crossing after the 30-min threshold: 54</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> negatives crossing: n=153 median=34.0 IQR=32.0-38.0 range=18-40 never_crossed=91; earliest 18 min; crossing after the 30-min threshold: 54</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  papGII positives: n=6 median=17.0 IQR=16.0-18.0 range=13-20 never_crossed=0</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> positives: n=6 median=17.0 IQR=16.0-18.0 range=13-20 never_crossed=0</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">  papGII negatives crossing: n=185 median=35.0 IQR=32.0-38.0 range=26-40 never_crossed=112; earliest 26 min; crossing after the 23-min threshold: 73</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> negatives crossing: n=185 median=35.0 IQR=32.0-38.0 range=26-40 never_crossed=112; earliest 26 min; crossing after the 23-min threshold: 73</t>
+          </r>
         </is>
       </c>
     </row>
@@ -15225,7 +16954,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B5" t="n">
@@ -15258,7 +16994,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B6" t="n">
@@ -15336,7 +17079,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>uidA</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
         </is>
       </c>
       <c r="B13" t="n">
@@ -15360,7 +17110,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>papGII</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>papGII</t>
+          </r>
         </is>
       </c>
       <c r="B14" t="n">
@@ -15409,7 +17166,43 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Supplementary Table 8. E. coli isolates of the clinical urine samples: phylogroup, mismatches at the LF binding site and uidA time to threshold.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Supplementary Table 8. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>E. coli</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> isolates of the clinical urine samples: phylogroup, mismatches at the LF binding site and </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>uidA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve"> time to threshold.</t>
+          </r>
         </is>
       </c>
     </row>
@@ -15484,7 +17277,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E5" t="n">
@@ -15519,7 +17319,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E6" t="n">
@@ -15554,7 +17361,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E7" t="n">
@@ -15589,7 +17403,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E8" t="n">
@@ -15624,7 +17445,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E9" t="n">
@@ -15659,7 +17487,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E10" t="n">
@@ -15694,7 +17529,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E11" t="n">
@@ -15729,7 +17571,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E12" t="n">
@@ -15764,7 +17613,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E13" t="n">
@@ -15799,7 +17655,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Proteus mirabilis, Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Proteus mirabilis</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E14" t="n">
@@ -15834,7 +17712,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E15" t="n">
@@ -15869,7 +17754,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E16" t="n">
@@ -15904,7 +17796,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E17" t="n">
@@ -15939,7 +17838,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E18" t="n">
@@ -15974,7 +17880,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E19" t="n">
@@ -16009,7 +17922,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E20" t="n">
@@ -16044,7 +17964,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E21" t="n">
@@ -16079,7 +18006,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E22" t="n">
@@ -16114,7 +18048,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E23" t="n">
@@ -16149,7 +18090,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E24" t="n">
@@ -16184,7 +18132,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E25" t="n">
@@ -16219,7 +18174,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E26" t="n">
@@ -16254,7 +18216,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E27" t="n">
@@ -16289,7 +18258,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E28" t="n">
@@ -16324,7 +18300,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E29" t="n">
@@ -16359,7 +18342,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Staphylococcus xylosus, Escherichia coli, Pantoea calida</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Staphylococcus xylosus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Pantoea calida</t>
+          </r>
         </is>
       </c>
       <c r="E30" t="n">
@@ -16394,7 +18414,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E31" t="n">
@@ -16429,7 +18456,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae, Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Klebsiella pneumoniae</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E32" t="n">
@@ -16464,7 +18513,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E33" t="n">
@@ -16499,7 +18555,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E34" t="n">
@@ -16534,7 +18597,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E35" t="n">
@@ -16569,7 +18639,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E36" t="n">
@@ -16604,7 +18681,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E37" t="n">
@@ -16639,7 +18723,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E38" t="n">
@@ -16674,7 +18765,29 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Enterococcus faecalis, Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Enterococcus faecalis</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E39" t="n">
@@ -16709,7 +18822,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Escherichia coli, Aerococcus urinae</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Aerococcus urinae</t>
+          </r>
         </is>
       </c>
       <c r="E40" t="n">
@@ -16744,7 +18879,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E41" t="n">
@@ -16779,15 +18921,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Escherichia coli</t>
+          </r>
         </is>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="b">
         <v>0</v>
       </c>

--- a/results/supplement/Supplementary_Tables.xlsx
+++ b/results/supplement/Supplementary_Tables.xlsx
@@ -1385,14 +1385,129 @@
     <t xml:space="preserve">LAMP191</t>
   </si>
   <si>
-    <r>
-      <rPr>
+    <t xml:space="preserve">Supplementary Table 2. Plate counts of the dilution series used for the limit of detection and the resulting bacterial densities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colonies per plate after plating 100, 10 and 1 ul of each dilution on COS agar. Densities were calculated from plates with 30-300 colonies; for 10^2 CFU/ml (&lt; 30 colonies) the count of the 100 ul plate is given as an estimate. The density of the 10^6 CFU/ml dilution was inferred from the 10^5 CFU/ml count (10-fold).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replicate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plated volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replicate 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 ul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">too many to count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 ul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 ul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replicate 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replicate 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^5: CFU/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^5: log10 difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^4: CFU/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^4: log10 difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^3: CFU/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^3: log10 difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^2: CFU/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10^2: log10 difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78e+05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32e+04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28e+03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50e+02 (&lt;30 colonies)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70e+04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53e+04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80e+02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20e+02 (&lt;30 colonies)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09e+05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22e+04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04e+03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00e+02 (&lt;30 colonies)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplementary Table 3. Median number of mismatches between the primers and their binding sites (UPEC + NCBI RefSeq genomes pooled; data of Figure 2A).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
         <sz val="11"/>
         <rFont val="Calibri"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Supplementary Table 2. </t>
+      <t xml:space="preserve">uidA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: per Clermont phylogroup (genomes with the target region present). </t>
     </r>
     <r>
       <rPr>
@@ -1402,7 +1517,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">uidA</t>
+      <t xml:space="preserve">papGII</t>
     </r>
     <r>
       <rPr>
@@ -1411,133 +1526,128 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: the ten highest-ranking results of the threshold search by Youden's index (191 samples).</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">All combinations of 40 time thresholds (1-40 min) and 200 fluorescence thresholds (fold-change relative to the first measurement; equally spaced between the lowest and highest observed value) were evaluated; combinations with the same classification result are summarised in one row. The selected thresholds (30 min, 3-fold) and the combination of 39 min and 11.4-fold are given below the table.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time thresholds giving this result (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluorescence thresholds (fold-change)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of combinations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specificity (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPV (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPV (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youden's index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4-11.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5-3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0-12.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2-12.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1-1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2-2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1-12.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7-13.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4-2.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1-11.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time threshold (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluorescence threshold (fold-change)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected (30 min, 3-fold)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39 min, 11.4-fold</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t xml:space="preserve">: per PapG class (best-matching </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
         <sz val="11"/>
         <rFont val="Calibri"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Supplementary Table 3. </t>
-    </r>
+      <t xml:space="preserve">papG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> locus of each genome), with minimum and maximum.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">phylogroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">genomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PapG-I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PapG-II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PapG-III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PapG-IV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm3plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uidA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">group</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -1555,16 +1665,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: diagnostic metrics at different time thresholds (fluorescence threshold &gt;= 3-fold change; 191 samples).</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">The selected time threshold of 23 min is the midpoint of the range (20-25 min) in which the Youden's index was 1.00.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplementary Table 4. Median number of mismatches between the primers and their binding sites (UPEC + NCBI RefSeq genomes pooled; data of Figure 2A).</t>
-  </si>
-  <si>
+      <t xml:space="preserve"> (alone or with </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -1573,7 +1675,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">uidA</t>
+      <t xml:space="preserve">papGIII</t>
     </r>
     <r>
       <rPr>
@@ -1582,7 +1684,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: per Clermont phylogroup (genomes with the target region present). </t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -1592,7 +1694,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">papGII</t>
+      <t xml:space="preserve">papGIV</t>
     </r>
     <r>
       <rPr>
@@ -1601,8 +1703,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: per PapG class (best-matching </t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -1611,6 +1715,57 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">papGIII</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> only</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">papGIV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> only</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">no </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">papG</t>
     </r>
     <r>
@@ -1620,350 +1775,18 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> locus of each genome), with minimum and maximum.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">phylogroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">genomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">allele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median</t>
-  </si>
-  <si>
-    <t xml:space="preserve">min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PapG-I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PapG-II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PapG-III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PapG-IV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mm0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mm1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mm2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mm3plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uidA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">group</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
+      <t xml:space="preserve"> allele</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">papGII</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (alone or with </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">papGIII</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">papGIV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">papGIII</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> only</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">papGIV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> only</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">no </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">papG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> allele</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplementary Table 5. Plate counts of the dilution series used for the limit of detection and the resulting bacterial densities.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colonies per plate after plating 100, 10 and 1 ul of each dilution on COS agar. Densities were calculated from plates with 30-300 colonies; for 10^2 CFU/ml (&lt; 30 colonies) the count of the 100 ul plate is given as an estimate. The density of the 10^6 CFU/ml dilution was inferred from the 10^5 CFU/ml count (10-fold).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Replicate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plated volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Replicate 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 ul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">too many to count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 ul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 ul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Replicate 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Replicate 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^5: CFU/ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^5: log10 difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^4: CFU/ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^4: log10 difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^3: CFU/ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^3: log10 difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^2: CFU/ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10^2: log10 difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78e+05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32e+04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28e+03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50e+02 (&lt;30 colonies)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70e+04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53e+04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80e+02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20e+02 (&lt;30 colonies)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09e+05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22e+04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04e+03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00e+02 (&lt;30 colonies)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Supplementary Table 6. Time to threshold of the 38 </t>
+      <t xml:space="preserve">Supplementary Table 4. Time to threshold of the 38 </t>
     </r>
     <r>
       <rPr>
@@ -2727,6 +2550,183 @@
       </rPr>
       <t xml:space="preserve"> negatives crossing: n=185 median=35.0 IQR=32.0-38.0 range=26-40 never_crossed=112; earliest 26 min; crossing after the 23-min threshold: 73</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Supplementary Table 5. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">uidA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: the ten highest-ranking results of the threshold search by Youden's index (191 samples).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">All combinations of 40 time thresholds (1-40 min) and 200 fluorescence thresholds (fold-change relative to the first measurement; equally spaced between the lowest and highest observed value) were evaluated; combinations with the same classification result are summarised in one row. The selected thresholds (30 min, 3-fold) and the combination of 39 min and 11.4-fold are given below the table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time thresholds giving this result (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluorescence thresholds (fold-change)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of combinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specificity (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPV (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPV (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youden's index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4-11.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5-3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0-12.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2-12.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1-1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2-2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1-12.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7-13.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4-2.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1-11.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time threshold (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluorescence threshold (fold-change)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected (30 min, 3-fold)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39 min, 11.4-fold</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Supplementary Table 6. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">papGII</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: diagnostic metrics at different time thresholds (fluorescence threshold &gt;= 3-fold change; 191 samples).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The selected time threshold of 23 min is the midpoint of the range (20-25 min) in which the Youden's index was 1.00.</t>
   </si>
   <si>
     <t xml:space="preserve">Supplementary Table 7. Bootstrap of the threshold selection (2,000 stratified resamples of the 191 samples).</t>
@@ -10194,6 +10194,3136 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>128</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>232</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>178</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>153</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>122</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>109</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H19" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H20" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K73"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" s="0" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>489</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>241</v>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>626</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="I52" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>506</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="I53" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="K53" s="0" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="F54" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>683</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>109</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>129</v>
+      </c>
+      <c r="F55" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>726</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>144</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>166</v>
+      </c>
+      <c r="F56" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>711</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>171</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>189</v>
+      </c>
+      <c r="F57" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>692</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="I57" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>205</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>224</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>462</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>265</v>
+      </c>
+      <c r="I58" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="F59" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="G59" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="H59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="F60" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="G60" s="0" t="n">
+        <v>139</v>
+      </c>
+      <c r="H60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="G61" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="H61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="G62" s="0" t="n">
+        <v>138</v>
+      </c>
+      <c r="H62" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>144</v>
+      </c>
+      <c r="F63" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="G63" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="H63" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="I63" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="D64" s="0" t="n">
+        <v>155</v>
+      </c>
+      <c r="E64" s="0" t="n">
+        <v>179</v>
+      </c>
+      <c r="F64" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="G64" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="H64" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="I64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="0" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="D65" s="0" t="n">
+        <v>181</v>
+      </c>
+      <c r="E65" s="0" t="n">
+        <v>199</v>
+      </c>
+      <c r="F65" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="G65" s="0" t="n">
+        <v>133</v>
+      </c>
+      <c r="H65" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I65" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="D66" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="E66" s="0" t="n">
+        <v>233</v>
+      </c>
+      <c r="F66" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="G66" s="0" t="n">
+        <v>118</v>
+      </c>
+      <c r="H66" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="I66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="E70" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="F70" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="G70" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="H70" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="I70" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="J70" s="0" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="D71" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="E71" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="F71" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="G71" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>474</v>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G74"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -10210,53 +13340,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>256</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>257</v>
+        <v>363</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>258</v>
+        <v>364</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>259</v>
+        <v>365</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>260</v>
+        <v>366</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>261</v>
+        <v>367</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>262</v>
+        <v>368</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>263</v>
+        <v>369</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>264</v>
+        <v>370</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>265</v>
+        <v>371</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>266</v>
+        <v>372</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>267</v>
+        <v>373</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>268</v>
+        <v>374</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>269</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10264,10 +13394,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>271</v>
+        <v>377</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>1</v>
@@ -10305,10 +13435,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>272</v>
+        <v>378</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>273</v>
+        <v>379</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>13</v>
@@ -10346,10 +13476,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>274</v>
+        <v>380</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>275</v>
+        <v>381</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>2</v>
@@ -10387,10 +13517,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>277</v>
+        <v>383</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>7</v>
@@ -10428,10 +13558,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>278</v>
+        <v>384</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>279</v>
+        <v>385</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>1</v>
@@ -10469,10 +13599,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>280</v>
+        <v>386</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>281</v>
+        <v>387</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>5</v>
@@ -10510,10 +13640,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>276</v>
+        <v>382</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>282</v>
+        <v>388</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>8</v>
@@ -10551,10 +13681,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>283</v>
+        <v>389</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>284</v>
+        <v>390</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>15</v>
@@ -10592,10 +13722,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>285</v>
+        <v>391</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>286</v>
+        <v>392</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>4</v>
@@ -10633,10 +13763,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>287</v>
+        <v>393</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>288</v>
+        <v>394</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>7</v>
@@ -10671,45 +13801,45 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>289</v>
+        <v>395</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>290</v>
+        <v>396</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>291</v>
+        <v>397</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>261</v>
+        <v>367</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>262</v>
+        <v>368</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>263</v>
+        <v>369</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>264</v>
+        <v>370</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>265</v>
+        <v>371</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>266</v>
+        <v>372</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>267</v>
+        <v>373</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>268</v>
+        <v>374</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>269</v>
+        <v>375</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>292</v>
+        <v>398</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>30</v>
@@ -10747,7 +13877,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>293</v>
+        <v>399</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>39</v>
@@ -10794,7 +13924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -10814,47 +13944,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>294</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>295</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>290</v>
+        <v>396</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>291</v>
+        <v>397</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>261</v>
+        <v>367</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>262</v>
+        <v>368</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>263</v>
+        <v>369</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>264</v>
+        <v>370</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>265</v>
+        <v>371</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>266</v>
+        <v>372</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>267</v>
+        <v>373</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>268</v>
+        <v>374</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>269</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11275,3136 +14405,6 @@
       </c>
       <c r="K16" s="0" t="n">
         <v>0.632</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:K73"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="0" t="n">
-        <v>1797</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="0" t="n">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="0" t="n">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="0" t="n">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="0" t="n">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>307</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="0" t="n">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="0" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="0" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="F16" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E17" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="C18" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E18" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>302</v>
-      </c>
-      <c r="C19" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="D19" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>300</v>
-      </c>
-      <c r="C20" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="F20" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>299</v>
-      </c>
-      <c r="C21" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="D22" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="C23" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="D23" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="C24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="0" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="0" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="C26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="0" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>302</v>
-      </c>
-      <c r="C27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="0" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>300</v>
-      </c>
-      <c r="C28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="0" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>299</v>
-      </c>
-      <c r="C29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="0" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="C30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="0" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="C31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="0" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="C32" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D32" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="F32" s="0" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E33" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="F33" s="0" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="C34" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="D34" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="E34" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="F34" s="0" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>302</v>
-      </c>
-      <c r="C35" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D35" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="F35" s="0" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>300</v>
-      </c>
-      <c r="C36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="0" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>299</v>
-      </c>
-      <c r="C37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="0" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="C38" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="D38" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="F38" s="0" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="C39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="0" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="C40" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="D40" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="F40" s="0" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D41" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E41" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="F41" s="0" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="C42" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="D42" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="E42" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="F42" s="0" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>302</v>
-      </c>
-      <c r="C43" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="D43" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="E43" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="F43" s="0" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>300</v>
-      </c>
-      <c r="C44" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D44" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E44" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="F44" s="0" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>299</v>
-      </c>
-      <c r="C45" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D45" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E45" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="F45" s="0" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="C46" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D46" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E46" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="F46" s="0" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="C47" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E47" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="F47" s="0" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>299</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="D51" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="F51" s="0" t="n">
-        <v>730</v>
-      </c>
-      <c r="G51" s="0" t="n">
-        <v>489</v>
-      </c>
-      <c r="H51" s="0" t="n">
-        <v>241</v>
-      </c>
-      <c r="I51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>300</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="D52" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="E52" s="0" t="n">
-        <v>43</v>
-      </c>
-      <c r="F52" s="0" t="n">
-        <v>730</v>
-      </c>
-      <c r="G52" s="0" t="n">
-        <v>626</v>
-      </c>
-      <c r="H52" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="I52" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="0" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B53" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="D53" s="0" t="n">
-        <v>54</v>
-      </c>
-      <c r="E53" s="0" t="n">
-        <v>71</v>
-      </c>
-      <c r="F53" s="0" t="n">
-        <v>730</v>
-      </c>
-      <c r="G53" s="0" t="n">
-        <v>506</v>
-      </c>
-      <c r="H53" s="0" t="n">
-        <v>85</v>
-      </c>
-      <c r="I53" s="0" t="n">
-        <v>88</v>
-      </c>
-      <c r="J53" s="0" t="n">
-        <v>51</v>
-      </c>
-      <c r="K53" s="0" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B54" s="0" t="s">
-        <v>302</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="D54" s="0" t="n">
-        <v>78</v>
-      </c>
-      <c r="E54" s="0" t="n">
-        <v>99</v>
-      </c>
-      <c r="F54" s="0" t="n">
-        <v>730</v>
-      </c>
-      <c r="G54" s="0" t="n">
-        <v>683</v>
-      </c>
-      <c r="H54" s="0" t="n">
-        <v>47</v>
-      </c>
-      <c r="I54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B55" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="D55" s="0" t="n">
-        <v>109</v>
-      </c>
-      <c r="E55" s="0" t="n">
-        <v>129</v>
-      </c>
-      <c r="F55" s="0" t="n">
-        <v>730</v>
-      </c>
-      <c r="G55" s="0" t="n">
-        <v>726</v>
-      </c>
-      <c r="H55" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B56" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="D56" s="0" t="n">
-        <v>144</v>
-      </c>
-      <c r="E56" s="0" t="n">
-        <v>166</v>
-      </c>
-      <c r="F56" s="0" t="n">
-        <v>730</v>
-      </c>
-      <c r="G56" s="0" t="n">
-        <v>711</v>
-      </c>
-      <c r="H56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="J56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B57" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="D57" s="0" t="n">
-        <v>171</v>
-      </c>
-      <c r="E57" s="0" t="n">
-        <v>189</v>
-      </c>
-      <c r="F57" s="0" t="n">
-        <v>730</v>
-      </c>
-      <c r="G57" s="0" t="n">
-        <v>692</v>
-      </c>
-      <c r="H57" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="I57" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B58" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="D58" s="0" t="n">
-        <v>205</v>
-      </c>
-      <c r="E58" s="0" t="n">
-        <v>224</v>
-      </c>
-      <c r="F58" s="0" t="n">
-        <v>730</v>
-      </c>
-      <c r="G58" s="0" t="n">
-        <v>462</v>
-      </c>
-      <c r="H58" s="0" t="n">
-        <v>265</v>
-      </c>
-      <c r="I58" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B59" s="0" t="s">
-        <v>299</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="D59" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="F59" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="G59" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="H59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" s="0" t="s">
-        <v>300</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="D60" s="0" t="n">
-        <v>38</v>
-      </c>
-      <c r="E60" s="0" t="n">
-        <v>60</v>
-      </c>
-      <c r="F60" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="G60" s="0" t="n">
-        <v>139</v>
-      </c>
-      <c r="H60" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B61" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="D61" s="0" t="n">
-        <v>61</v>
-      </c>
-      <c r="E61" s="0" t="n">
-        <v>85</v>
-      </c>
-      <c r="F61" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="G61" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="H61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B62" s="0" t="s">
-        <v>302</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="D62" s="0" t="n">
-        <v>90</v>
-      </c>
-      <c r="E62" s="0" t="n">
-        <v>111</v>
-      </c>
-      <c r="F62" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="G62" s="0" t="n">
-        <v>138</v>
-      </c>
-      <c r="H62" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B63" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="D63" s="0" t="n">
-        <v>120</v>
-      </c>
-      <c r="E63" s="0" t="n">
-        <v>144</v>
-      </c>
-      <c r="F63" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="G63" s="0" t="n">
-        <v>70</v>
-      </c>
-      <c r="H63" s="0" t="n">
-        <v>68</v>
-      </c>
-      <c r="I63" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B64" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="D64" s="0" t="n">
-        <v>155</v>
-      </c>
-      <c r="E64" s="0" t="n">
-        <v>179</v>
-      </c>
-      <c r="F64" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="G64" s="0" t="n">
-        <v>107</v>
-      </c>
-      <c r="H64" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="I64" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="0" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B65" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="D65" s="0" t="n">
-        <v>181</v>
-      </c>
-      <c r="E65" s="0" t="n">
-        <v>199</v>
-      </c>
-      <c r="F65" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="G65" s="0" t="n">
-        <v>133</v>
-      </c>
-      <c r="H65" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="I65" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B66" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="D66" s="0" t="n">
-        <v>212</v>
-      </c>
-      <c r="E66" s="0" t="n">
-        <v>233</v>
-      </c>
-      <c r="F66" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="G66" s="0" t="n">
-        <v>118</v>
-      </c>
-      <c r="H66" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="I66" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B70" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="C70" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="D70" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="E70" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="F70" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="G70" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="H70" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="I70" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="J70" s="0" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B71" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="C71" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="D71" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="E71" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="F71" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="G71" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B72" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="C72" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B73" s="0" t="n">
-        <v>474</v>
-      </c>
-      <c r="C73" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>128</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>232</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>178</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>34</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>98</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="E9" s="0" t="n">
-        <v>153</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>97</v>
-      </c>
-      <c r="E10" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="E12" s="0" t="n">
-        <v>122</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>109</v>
-      </c>
-      <c r="E13" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>357</v>
-      </c>
-      <c r="C18" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>358</v>
-      </c>
-      <c r="E18" s="0" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>359</v>
-      </c>
-      <c r="G18" s="0" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="I18" s="0" t="n">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>361</v>
-      </c>
-      <c r="C19" s="0" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>362</v>
-      </c>
-      <c r="E19" s="0" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F19" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="G19" s="0" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H19" s="0" t="s">
-        <v>364</v>
-      </c>
-      <c r="I19" s="0" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="C20" s="0" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>366</v>
-      </c>
-      <c r="E20" s="0" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>367</v>
-      </c>
-      <c r="G20" s="0" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H20" s="0" t="s">
-        <v>368</v>
-      </c>
-      <c r="I20" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G74"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="G16" s="0" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="0" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="G18" s="0" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="G19" s="0" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="G20" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="0" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="0" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="0" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="0" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="0" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="0" t="n">
-        <v>26</v>
-      </c>
-      <c r="G26" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>243</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="0" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="0" t="n">
-        <v>26</v>
-      </c>
-      <c r="G28" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="0" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="0" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="0" t="n">
-        <v>27</v>
-      </c>
-      <c r="G31" s="0" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="0" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="0" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="G34" s="0" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="0" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="G36" s="0" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="0" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="G38" s="0" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="0" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="D40" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="0" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="0" t="n">
-        <v>36</v>
-      </c>
-      <c r="G41" s="0" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -14478,7 +14478,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>30</v>
@@ -14564,7 +14564,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>36</v>
@@ -14656,7 +14656,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>425</v>
